--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381565</v>
+        <v>122380454</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,39 +828,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482013</v>
+        <v>481961</v>
       </c>
       <c r="R3" t="n">
-        <v>6989214</v>
+        <v>6988882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -944,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381462</v>
+        <v>122380586</v>
       </c>
       <c r="B4" t="n">
         <v>78645</v>
@@ -978,21 +948,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481994</v>
+        <v>481966</v>
       </c>
       <c r="R4" t="n">
-        <v>6989021</v>
+        <v>6988824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,11 +992,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1040,31 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1081,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122380454</v>
+        <v>122381042</v>
       </c>
       <c r="B5" t="n">
         <v>78645</v>
@@ -1121,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481961</v>
+        <v>481916</v>
       </c>
       <c r="R5" t="n">
-        <v>6988882</v>
+        <v>6988986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,6 +1102,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380586</v>
+        <v>122380476</v>
       </c>
       <c r="B6" t="n">
         <v>78645</v>
@@ -1219,14 +1179,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481966</v>
+        <v>481964</v>
       </c>
       <c r="R6" t="n">
-        <v>6988824</v>
+        <v>6988862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381042</v>
+        <v>122380777</v>
       </c>
       <c r="B7" t="n">
         <v>78645</v>
@@ -1325,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481916</v>
+        <v>481960</v>
       </c>
       <c r="R7" t="n">
-        <v>6988986</v>
+        <v>6988961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,31 +1331,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1412,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122380777</v>
+        <v>122381411</v>
       </c>
       <c r="B8" t="n">
         <v>78645</v>
@@ -1452,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481960</v>
+        <v>481939</v>
       </c>
       <c r="R8" t="n">
-        <v>6988961</v>
+        <v>6989076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,6 +1425,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1498,6 +1438,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1514,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122380476</v>
+        <v>122397557</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>90779</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,37 +1495,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481964</v>
+        <v>482021</v>
       </c>
       <c r="R9" t="n">
-        <v>6988862</v>
+        <v>6989225</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,14 +1564,45 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1616,7 +1619,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381411</v>
+        <v>122381462</v>
       </c>
       <c r="B10" t="n">
         <v>78645</v>
@@ -1650,16 +1653,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481939</v>
+        <v>481994</v>
       </c>
       <c r="R10" t="n">
-        <v>6989076</v>
+        <v>6989021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1704,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,12 +1733,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1745,6 +1753,277 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122397158</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78645</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Håkansgårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481974</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6989025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122381565</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90797</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>482013</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6989214</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122380454</v>
+        <v>122381411</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481961</v>
+        <v>481939</v>
       </c>
       <c r="R3" t="n">
-        <v>6988882</v>
+        <v>6989076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,6 +890,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,6 +903,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380586</v>
+        <v>122380777</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,14 +980,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481966</v>
+        <v>481960</v>
       </c>
       <c r="R4" t="n">
-        <v>6988824</v>
+        <v>6988961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1049,7 @@
         <v>122381042</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1143,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380476</v>
+        <v>122380454</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481964</v>
+        <v>481961</v>
       </c>
       <c r="R6" t="n">
-        <v>6988862</v>
+        <v>6988882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122380777</v>
+        <v>122380476</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481960</v>
+        <v>481964</v>
       </c>
       <c r="R7" t="n">
-        <v>6988961</v>
+        <v>6988862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381411</v>
+        <v>122380586</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,14 +1413,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481939</v>
+        <v>481966</v>
       </c>
       <c r="R8" t="n">
-        <v>6989076</v>
+        <v>6988824</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,11 +1455,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1438,31 +1463,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122397557</v>
+        <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>90779</v>
+        <v>90807</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,17 +1522,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482021</v>
+        <v>482013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989225</v>
+        <v>6989214</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,11 +1562,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1622,7 +1617,7 @@
         <v>122381462</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1756,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>90789</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,26 +1767,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1799,13 +1798,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R11" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,7 +1838,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,12 +1868,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1892,10 +1891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381565</v>
+        <v>122397158</v>
       </c>
       <c r="B12" t="n">
-        <v>90797</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1908,41 +1907,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482013</v>
+        <v>481974</v>
       </c>
       <c r="R12" t="n">
-        <v>6989214</v>
+        <v>6989025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,6 +1972,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122381645</v>
+        <v>122380586</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482002</v>
+        <v>481966</v>
       </c>
       <c r="R2" t="n">
-        <v>6989234</v>
+        <v>6988824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381411</v>
+        <v>122381645</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481939</v>
+        <v>482002</v>
       </c>
       <c r="R3" t="n">
-        <v>6989076</v>
+        <v>6989234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar. Långväxta bålar.</t>
+          <t>Rejäla hackspår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +881,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380777</v>
+        <v>122381042</v>
       </c>
       <c r="B4" t="n">
         <v>78646</v>
@@ -984,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481960</v>
+        <v>481916</v>
       </c>
       <c r="R4" t="n">
-        <v>6988961</v>
+        <v>6988986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,6 +1000,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381042</v>
+        <v>122380454</v>
       </c>
       <c r="B5" t="n">
         <v>78646</v>
@@ -1086,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481916</v>
+        <v>481961</v>
       </c>
       <c r="R5" t="n">
-        <v>6988986</v>
+        <v>6988882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,31 +1127,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380454</v>
+        <v>122381411</v>
       </c>
       <c r="B6" t="n">
         <v>78646</v>
@@ -1213,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481961</v>
+        <v>481939</v>
       </c>
       <c r="R6" t="n">
-        <v>6988882</v>
+        <v>6989076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,6 +1221,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1259,6 +1234,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122380586</v>
+        <v>122380777</v>
       </c>
       <c r="B8" t="n">
         <v>78646</v>
@@ -1413,14 +1413,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481966</v>
+        <v>481960</v>
       </c>
       <c r="R8" t="n">
-        <v>6988824</v>
+        <v>6988961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381565</v>
+        <v>122397557</v>
       </c>
       <c r="B9" t="n">
-        <v>90807</v>
+        <v>90789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,17 +1522,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482013</v>
+        <v>482021</v>
       </c>
       <c r="R9" t="n">
-        <v>6989214</v>
+        <v>6989225</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,6 +1562,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1751,10 +1756,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397557</v>
+        <v>122381565</v>
       </c>
       <c r="B11" t="n">
-        <v>90789</v>
+        <v>90807</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,21 +1772,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1794,17 +1799,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482021</v>
+        <v>482013</v>
       </c>
       <c r="R11" t="n">
-        <v>6989225</v>
+        <v>6989214</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,11 +1839,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380586</v>
+        <v>122381645</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481966</v>
+        <v>482002</v>
       </c>
       <c r="R2" t="n">
-        <v>6988824</v>
+        <v>6989234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381645</v>
+        <v>122380586</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +828,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482002</v>
+        <v>481966</v>
       </c>
       <c r="R3" t="n">
-        <v>6989234</v>
+        <v>6988824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,11 +890,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381042</v>
+        <v>122381411</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481916</v>
+        <v>481939</v>
       </c>
       <c r="R4" t="n">
-        <v>6988986</v>
+        <v>6989076</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,6 +990,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122380454</v>
+        <v>122380476</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481961</v>
+        <v>481964</v>
       </c>
       <c r="R5" t="n">
-        <v>6988882</v>
+        <v>6988862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381411</v>
+        <v>122380454</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481939</v>
+        <v>481961</v>
       </c>
       <c r="R6" t="n">
-        <v>6989076</v>
+        <v>6988882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,11 +1226,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1234,31 +1234,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1275,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122380476</v>
+        <v>122380777</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481964</v>
+        <v>481960</v>
       </c>
       <c r="R7" t="n">
-        <v>6988862</v>
+        <v>6988961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122380777</v>
+        <v>122381042</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481960</v>
+        <v>481916</v>
       </c>
       <c r="R8" t="n">
-        <v>6988961</v>
+        <v>6988986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,6 +1438,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122397557</v>
+        <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>90789</v>
+        <v>90819</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,17 +1522,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482021</v>
+        <v>482013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989225</v>
+        <v>6989214</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,11 +1562,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1619,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381462</v>
+        <v>122397557</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>90801</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,42 +1630,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481994</v>
+        <v>482021</v>
       </c>
       <c r="R10" t="n">
-        <v>6989021</v>
+        <v>6989225</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1701,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,6 +1710,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1733,12 +1731,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1756,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122381565</v>
+        <v>122397158</v>
       </c>
       <c r="B11" t="n">
-        <v>90807</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,41 +1770,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482013</v>
+        <v>481974</v>
       </c>
       <c r="R11" t="n">
-        <v>6989214</v>
+        <v>6989025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,6 +1835,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1868,12 +1867,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1891,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397158</v>
+        <v>122381462</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1925,19 +1924,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481974</v>
+        <v>481994</v>
       </c>
       <c r="R12" t="n">
-        <v>6989025</v>
+        <v>6989021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1983,7 +1984,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122381645</v>
+        <v>122380586</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482002</v>
+        <v>481966</v>
       </c>
       <c r="R2" t="n">
-        <v>6989234</v>
+        <v>6988824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122380586</v>
+        <v>122381411</v>
       </c>
       <c r="B3" t="n">
         <v>78651</v>
@@ -848,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481966</v>
+        <v>481939</v>
       </c>
       <c r="R3" t="n">
-        <v>6988824</v>
+        <v>6989076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,6 +855,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,6 +868,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381411</v>
+        <v>122380454</v>
       </c>
       <c r="B4" t="n">
         <v>78651</v>
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481939</v>
+        <v>481961</v>
       </c>
       <c r="R4" t="n">
-        <v>6989076</v>
+        <v>6988882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,11 +987,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,31 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122380476</v>
+        <v>122381042</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1086,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481964</v>
+        <v>481916</v>
       </c>
       <c r="R5" t="n">
-        <v>6988862</v>
+        <v>6988986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,6 +1097,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380454</v>
+        <v>122380476</v>
       </c>
       <c r="B6" t="n">
         <v>78651</v>
@@ -1188,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481961</v>
+        <v>481964</v>
       </c>
       <c r="R6" t="n">
-        <v>6988882</v>
+        <v>6988862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1352,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381042</v>
+        <v>122381645</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1358,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481916</v>
+        <v>482002</v>
       </c>
       <c r="R8" t="n">
-        <v>6988986</v>
+        <v>6989234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,6 +1425,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1446,22 +1446,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
         <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397557</v>
+        <v>122397158</v>
       </c>
       <c r="B10" t="n">
-        <v>90801</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,30 +1630,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1661,13 +1657,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482021</v>
+        <v>481974</v>
       </c>
       <c r="R10" t="n">
-        <v>6989225</v>
+        <v>6989025</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1697,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,12 +1727,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1754,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>90808</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,26 +1766,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R11" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380586</v>
+        <v>122381411</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481966</v>
+        <v>481939</v>
       </c>
       <c r="R2" t="n">
-        <v>6988824</v>
+        <v>6989076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +748,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381411</v>
+        <v>122380454</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +815,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481939</v>
+        <v>481961</v>
       </c>
       <c r="R3" t="n">
-        <v>6989076</v>
+        <v>6988882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +870,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -868,31 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380454</v>
+        <v>122380777</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,11 +912,6 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -949,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481961</v>
+        <v>481960</v>
       </c>
       <c r="R4" t="n">
-        <v>6988882</v>
+        <v>6988961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381042</v>
+        <v>122380476</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,11 +1009,6 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1051,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481916</v>
+        <v>481964</v>
       </c>
       <c r="R5" t="n">
-        <v>6988986</v>
+        <v>6988862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,31 +1072,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380476</v>
+        <v>122380586</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,11 +1106,6 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1174,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481964</v>
+        <v>481966</v>
       </c>
       <c r="R6" t="n">
-        <v>6988862</v>
+        <v>6988824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122380777</v>
+        <v>122381645</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481960</v>
+        <v>482002</v>
       </c>
       <c r="R7" t="n">
-        <v>6988961</v>
+        <v>6989234</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,6 +1263,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1326,6 +1276,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1342,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381645</v>
+        <v>122381042</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,39 +1328,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482002</v>
+        <v>481916</v>
       </c>
       <c r="R8" t="n">
-        <v>6989234</v>
+        <v>6988986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,11 +1385,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1444,24 +1399,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1479,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381565</v>
+        <v>122381462</v>
       </c>
       <c r="B9" t="n">
-        <v>90826</v>
+        <v>78652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,41 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482013</v>
+        <v>481994</v>
       </c>
       <c r="R9" t="n">
-        <v>6989214</v>
+        <v>6989021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,13 +1507,17 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1579,11 +1526,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1591,12 +1533,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1614,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>90813</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,26 +1572,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1657,13 +1598,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R10" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1638,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,11 +1656,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1727,12 +1663,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1750,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397557</v>
+        <v>122381565</v>
       </c>
       <c r="B11" t="n">
-        <v>90808</v>
+        <v>90831</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,21 +1702,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,17 +1724,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482021</v>
+        <v>482013</v>
       </c>
       <c r="R11" t="n">
-        <v>6989225</v>
+        <v>6989214</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1833,11 +1764,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,11 +1781,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1872,7 +1793,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,10 +1811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381462</v>
+        <v>122397158</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1908,11 +1829,6 @@
       <c r="E12" t="n">
         <v>6425</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1924,21 +1840,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481994</v>
+        <v>481974</v>
       </c>
       <c r="R12" t="n">
-        <v>6989021</v>
+        <v>6989025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,17 +1898,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122381411</v>
+        <v>122380777</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481939</v>
+        <v>481960</v>
       </c>
       <c r="R2" t="n">
-        <v>6989076</v>
+        <v>6988961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +753,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -800,7 +780,7 @@
         <v>122380454</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -894,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380777</v>
+        <v>122380586</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,6 +897,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -925,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481960</v>
+        <v>481966</v>
       </c>
       <c r="R4" t="n">
-        <v>6988961</v>
+        <v>6988824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122380476</v>
+        <v>122381042</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,6 +999,11 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481964</v>
+        <v>481916</v>
       </c>
       <c r="R5" t="n">
-        <v>6988862</v>
+        <v>6988986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1088,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380586</v>
+        <v>122380476</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1106,6 +1126,11 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1119,14 +1144,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481966</v>
+        <v>481964</v>
       </c>
       <c r="R6" t="n">
-        <v>6988824</v>
+        <v>6988862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1213,7 @@
         <v>122381645</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,6 +1228,11 @@
       <c r="E7" t="n">
         <v>100049</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1280,6 +1310,11 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1312,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381042</v>
+        <v>122381411</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,6 +1365,11 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1347,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481916</v>
+        <v>481939</v>
       </c>
       <c r="R8" t="n">
-        <v>6988986</v>
+        <v>6989076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1425,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1397,6 +1442,11 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1429,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381462</v>
+        <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,34 +1495,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481994</v>
+        <v>482013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989021</v>
+        <v>6989214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,17 +1564,13 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1526,6 +1579,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1533,12 +1591,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1556,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397557</v>
+        <v>122381462</v>
       </c>
       <c r="B10" t="n">
-        <v>90813</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,39 +1630,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482021</v>
+        <v>481994</v>
       </c>
       <c r="R10" t="n">
-        <v>6989225</v>
+        <v>6989021</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1699,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,7 +1708,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1656,6 +1716,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1663,12 +1728,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1686,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122381565</v>
+        <v>122397158</v>
       </c>
       <c r="B11" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,36 +1767,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482013</v>
+        <v>481974</v>
       </c>
       <c r="R11" t="n">
-        <v>6989214</v>
+        <v>6989025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,6 +1832,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1781,6 +1852,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1788,12 +1864,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1811,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>90826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1903,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1849,13 +1934,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R12" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,7 +1974,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,6 +1992,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -1914,12 +2004,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380777</v>
+        <v>122380454</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481960</v>
+        <v>481961</v>
       </c>
       <c r="R2" t="n">
-        <v>6988961</v>
+        <v>6988882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122380454</v>
+        <v>122380777</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481961</v>
+        <v>481960</v>
       </c>
       <c r="R3" t="n">
-        <v>6988882</v>
+        <v>6988961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380586</v>
+        <v>122381042</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -915,14 +915,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481966</v>
+        <v>481916</v>
       </c>
       <c r="R4" t="n">
-        <v>6988824</v>
+        <v>6988986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -981,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381042</v>
+        <v>122381645</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481916</v>
+        <v>482002</v>
       </c>
       <c r="R5" t="n">
-        <v>6988986</v>
+        <v>6989234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,6 +1089,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1075,22 +1110,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380476</v>
+        <v>122380586</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1144,14 +1179,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481964</v>
+        <v>481966</v>
       </c>
       <c r="R6" t="n">
-        <v>6988862</v>
+        <v>6988824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381645</v>
+        <v>122381411</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482002</v>
+        <v>481939</v>
       </c>
       <c r="R7" t="n">
-        <v>6989234</v>
+        <v>6989076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1325,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,22 +1344,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1347,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381411</v>
+        <v>122380476</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1387,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481939</v>
+        <v>481964</v>
       </c>
       <c r="R8" t="n">
-        <v>6989076</v>
+        <v>6988862</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,11 +1455,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1438,31 +1463,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1482,7 +1482,7 @@
         <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381462</v>
+        <v>122397158</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1648,21 +1648,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481994</v>
+        <v>481974</v>
       </c>
       <c r="R10" t="n">
-        <v>6989021</v>
+        <v>6989025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,6 +1706,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,26 +1766,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1794,13 +1797,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R11" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1864,12 +1867,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1887,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397557</v>
+        <v>122381462</v>
       </c>
       <c r="B12" t="n">
-        <v>90826</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1903,44 +1906,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482021</v>
+        <v>481994</v>
       </c>
       <c r="R12" t="n">
-        <v>6989225</v>
+        <v>6989021</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,7 +1975,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,7 +1984,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380454</v>
+        <v>122381042</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481961</v>
+        <v>481916</v>
       </c>
       <c r="R2" t="n">
-        <v>6988882</v>
+        <v>6988986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122380777</v>
+        <v>122381645</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481960</v>
+        <v>482002</v>
       </c>
       <c r="R3" t="n">
-        <v>6988961</v>
+        <v>6989234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +885,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,6 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381042</v>
+        <v>122380586</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -915,14 +975,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481916</v>
+        <v>481966</v>
       </c>
       <c r="R4" t="n">
-        <v>6988986</v>
+        <v>6988824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,31 +1025,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381645</v>
+        <v>122381411</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,39 +1057,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482002</v>
+        <v>481939</v>
       </c>
       <c r="R5" t="n">
-        <v>6989234</v>
+        <v>6989076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1140,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380586</v>
+        <v>122380476</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1179,14 +1209,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481966</v>
+        <v>481964</v>
       </c>
       <c r="R6" t="n">
-        <v>6988824</v>
+        <v>6988862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381411</v>
+        <v>122380454</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1285,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481939</v>
+        <v>481961</v>
       </c>
       <c r="R7" t="n">
-        <v>6989076</v>
+        <v>6988882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,11 +1353,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1336,31 +1361,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122380476</v>
+        <v>122380777</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481964</v>
+        <v>481960</v>
       </c>
       <c r="R8" t="n">
-        <v>6988862</v>
+        <v>6988961</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,26 +1630,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1657,13 +1661,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R10" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,12 +1731,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1750,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397557</v>
+        <v>122381462</v>
       </c>
       <c r="B11" t="n">
-        <v>90839</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,44 +1770,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482021</v>
+        <v>481994</v>
       </c>
       <c r="R11" t="n">
-        <v>6989225</v>
+        <v>6989021</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,7 +1839,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,7 +1848,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1867,12 +1868,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,7 +1891,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381462</v>
+        <v>122397158</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1924,21 +1925,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481994</v>
+        <v>481974</v>
       </c>
       <c r="R12" t="n">
-        <v>6989021</v>
+        <v>6989025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,6 +1983,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381645</v>
+        <v>122380454</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,39 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482002</v>
+        <v>481961</v>
       </c>
       <c r="R3" t="n">
-        <v>6989234</v>
+        <v>6988882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,11 +880,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -898,31 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -939,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380586</v>
+        <v>122381645</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481966</v>
+        <v>482002</v>
       </c>
       <c r="R4" t="n">
-        <v>6988824</v>
+        <v>6989234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,6 +987,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1025,6 +1000,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122381411</v>
+        <v>122380586</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1077,14 +1077,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481939</v>
+        <v>481966</v>
       </c>
       <c r="R5" t="n">
-        <v>6989076</v>
+        <v>6988824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,11 +1119,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,31 +1127,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1275,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122380454</v>
+        <v>122381411</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1315,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481961</v>
+        <v>481939</v>
       </c>
       <c r="R7" t="n">
-        <v>6988882</v>
+        <v>6989076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,6 +1323,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1361,6 +1336,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381565</v>
+        <v>122397158</v>
       </c>
       <c r="B9" t="n">
-        <v>90857</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,41 +1495,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482013</v>
+        <v>481974</v>
       </c>
       <c r="R9" t="n">
-        <v>6989214</v>
+        <v>6989025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,6 +1560,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1591,12 +1592,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1614,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397557</v>
+        <v>122381565</v>
       </c>
       <c r="B10" t="n">
-        <v>90839</v>
+        <v>90851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,21 +1631,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1657,17 +1658,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482021</v>
+        <v>482013</v>
       </c>
       <c r="R10" t="n">
-        <v>6989225</v>
+        <v>6989214</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,11 +1698,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,7 +1732,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1891,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,26 +1903,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R12" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122381042</v>
+        <v>122380777</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481916</v>
+        <v>481960</v>
       </c>
       <c r="R2" t="n">
-        <v>6988986</v>
+        <v>6988961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122380454</v>
+        <v>122381042</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -842,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481961</v>
+        <v>481916</v>
       </c>
       <c r="R3" t="n">
-        <v>6988882</v>
+        <v>6988986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,6 +863,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122381645</v>
+        <v>122380476</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482002</v>
+        <v>481964</v>
       </c>
       <c r="R4" t="n">
-        <v>6989234</v>
+        <v>6988862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,11 +982,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,31 +990,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,7 +1006,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122380586</v>
+        <v>122380454</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1077,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481966</v>
+        <v>481961</v>
       </c>
       <c r="R5" t="n">
-        <v>6988824</v>
+        <v>6988882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380476</v>
+        <v>122380586</v>
       </c>
       <c r="B6" t="n">
         <v>78656</v>
@@ -1179,14 +1144,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481964</v>
+        <v>481966</v>
       </c>
       <c r="R6" t="n">
-        <v>6988862</v>
+        <v>6988824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1377,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122380777</v>
+        <v>122381645</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,34 +1358,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481960</v>
+        <v>482002</v>
       </c>
       <c r="R8" t="n">
-        <v>6988961</v>
+        <v>6989234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,6 +1425,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,6 +1438,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122397158</v>
+        <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,37 +1495,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481974</v>
+        <v>482013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989025</v>
+        <v>6989214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,11 +1564,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1592,12 +1591,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1615,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381565</v>
+        <v>122397557</v>
       </c>
       <c r="B10" t="n">
-        <v>90851</v>
+        <v>90833</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,21 +1630,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,17 +1657,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482013</v>
+        <v>482021</v>
       </c>
       <c r="R10" t="n">
-        <v>6989214</v>
+        <v>6989225</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,6 +1697,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,7 +1736,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1750,7 +1754,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122381462</v>
+        <v>122397158</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1784,21 +1788,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481994</v>
+        <v>481974</v>
       </c>
       <c r="R11" t="n">
-        <v>6989021</v>
+        <v>6989025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,6 +1846,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1887,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397557</v>
+        <v>122381462</v>
       </c>
       <c r="B12" t="n">
-        <v>90833</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1903,44 +1906,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482021</v>
+        <v>481994</v>
       </c>
       <c r="R12" t="n">
-        <v>6989225</v>
+        <v>6989021</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1974,7 +1975,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,7 +1984,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380777</v>
+        <v>122380476</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481960</v>
+        <v>481964</v>
       </c>
       <c r="R2" t="n">
-        <v>6988961</v>
+        <v>6988862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381042</v>
+        <v>122381645</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481916</v>
+        <v>482002</v>
       </c>
       <c r="R3" t="n">
-        <v>6988986</v>
+        <v>6989234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +860,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,22 +881,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122380476</v>
+        <v>122380777</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481964</v>
+        <v>481960</v>
       </c>
       <c r="R4" t="n">
-        <v>6988862</v>
+        <v>6988961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1019,7 @@
         <v>122380454</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1111,7 +1121,7 @@
         <v>122380586</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381411</v>
+        <v>122381042</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481939</v>
+        <v>481916</v>
       </c>
       <c r="R7" t="n">
-        <v>6989076</v>
+        <v>6988986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1296,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381645</v>
+        <v>122381411</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,39 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482002</v>
+        <v>481939</v>
       </c>
       <c r="R8" t="n">
-        <v>6989234</v>
+        <v>6989076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rejäla hackspår.</t>
+          <t>På flera granar. Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381565</v>
+        <v>122381462</v>
       </c>
       <c r="B9" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,41 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482013</v>
+        <v>481994</v>
       </c>
       <c r="R9" t="n">
-        <v>6989214</v>
+        <v>6989021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,13 +1562,17 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1591,12 +1593,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1614,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397557</v>
+        <v>122381565</v>
       </c>
       <c r="B10" t="n">
-        <v>90833</v>
+        <v>90852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,21 +1632,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1657,17 +1659,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482021</v>
+        <v>482013</v>
       </c>
       <c r="R10" t="n">
-        <v>6989225</v>
+        <v>6989214</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,11 +1699,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,7 +1733,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1754,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122397158</v>
+        <v>122397557</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>90834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,26 +1767,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1797,13 +1798,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481974</v>
+        <v>482021</v>
       </c>
       <c r="R11" t="n">
-        <v>6989025</v>
+        <v>6989225</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,7 +1838,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Vidsträckt fruktkropp på en stående granhögstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,12 +1868,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,10 +1891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122381462</v>
+        <v>122397158</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1924,21 +1925,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481994</v>
+        <v>481974</v>
       </c>
       <c r="R12" t="n">
-        <v>6989021</v>
+        <v>6989025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,6 +1983,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380476</v>
+        <v>122380586</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481964</v>
+        <v>481966</v>
       </c>
       <c r="R2" t="n">
-        <v>6988862</v>
+        <v>6988824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122381645</v>
+        <v>122380454</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482002</v>
+        <v>481961</v>
       </c>
       <c r="R3" t="n">
-        <v>6989234</v>
+        <v>6988882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,11 +855,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,7 +882,7 @@
         <v>122380777</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122380454</v>
+        <v>122380476</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481961</v>
+        <v>481964</v>
       </c>
       <c r="R5" t="n">
-        <v>6988882</v>
+        <v>6988862</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122380586</v>
+        <v>122381042</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481966</v>
+        <v>481916</v>
       </c>
       <c r="R6" t="n">
-        <v>6988824</v>
+        <v>6988986</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1169,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1220,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381042</v>
+        <v>122381645</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481916</v>
+        <v>482002</v>
       </c>
       <c r="R7" t="n">
-        <v>6988986</v>
+        <v>6989234</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,6 +1293,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1314,22 +1314,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
         <v>122381411</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381462</v>
+        <v>122381565</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1495,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481994</v>
+        <v>482013</v>
       </c>
       <c r="R9" t="n">
-        <v>6989021</v>
+        <v>6989214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,17 +1564,13 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1593,12 +1591,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1616,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122381565</v>
+        <v>122381462</v>
       </c>
       <c r="B10" t="n">
-        <v>90852</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,41 +1630,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482013</v>
+        <v>481994</v>
       </c>
       <c r="R10" t="n">
-        <v>6989214</v>
+        <v>6989021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,13 +1697,17 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1754,7 +1754,7 @@
         <v>122397557</v>
       </c>
       <c r="B11" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>122397158</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 60109-2024 artfynd.xlsx
+++ b/artfynd/A 60109-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122380586</v>
+        <v>122381411</v>
       </c>
       <c r="B2" t="n">
         <v>78660</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481966</v>
+        <v>481939</v>
       </c>
       <c r="R2" t="n">
-        <v>6988824</v>
+        <v>6989076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +753,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På flera granar. Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +766,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122380454</v>
+        <v>122380586</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -813,14 +843,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Israelsbodarna, Israelsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481961</v>
+        <v>481966</v>
       </c>
       <c r="R3" t="n">
-        <v>6988882</v>
+        <v>6988824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122381042</v>
+        <v>122381645</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1129,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481916</v>
+        <v>482002</v>
       </c>
       <c r="R6" t="n">
-        <v>6988986</v>
+        <v>6989234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,6 +1196,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1177,22 +1217,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1210,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122381645</v>
+        <v>122381042</v>
       </c>
       <c r="B7" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482002</v>
+        <v>481916</v>
       </c>
       <c r="R7" t="n">
-        <v>6989234</v>
+        <v>6988986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,11 +1328,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1314,22 +1344,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1347,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122381411</v>
+        <v>122380454</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1387,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481939</v>
+        <v>481961</v>
       </c>
       <c r="R8" t="n">
-        <v>6989076</v>
+        <v>6988882</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,11 +1455,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På flera granar. Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1438,31 +1463,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122381565</v>
+        <v>122397158</v>
       </c>
       <c r="B9" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,41 +1495,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482013</v>
+        <v>481974</v>
       </c>
       <c r="R9" t="n">
-        <v>6989214</v>
+        <v>6989025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,6 +1560,11 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1591,12 +1592,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1891,10 +1892,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397158</v>
+        <v>122381565</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,37 +1908,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Håkansgårdsbodarna, Jmt</t>
+          <t>Håkansgårdsbodarna, Håkansgårdsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481974</v>
+        <v>482013</v>
       </c>
       <c r="R12" t="n">
-        <v>6989025</v>
+        <v>6989214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1972,11 +1977,6 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # På högstubbe och även en granlåga intill. # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
